--- a/data/merged/2026-09-23/MERGED_DE_Mite-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_DE_Mite-Vacuum_2026-09-23.xlsx
@@ -7195,50 +7195,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7564,7 +7520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -18635,40 +18591,40 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0GH912PFJ</t>
+          <t>B0D9BQHSWQ</t>
         </is>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/stores/K%C3%A4rcher/page/EFE3653A-1163-432C-A85B-0486A31C0E3D?lp_asin=B0GH912PFJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.de/stores/Jimmy/page/5E6E99F6-7A7E-4436-AC80-BC0EF24EA864?lp_asin=B0D9BQHSWQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER Filter-Set für VCH 4 UVClean Matratzenreiniger, Ersatzfilter aus Motorschutzfilter und Schaumfilter für hygienische R</t>
+          <t>Jimmy Milbensauger für Matratzen 15kPa Matratzensauger mit Staubsensor, Heißluftfunktion, UV-C Licht, Ultraschall-Technik, Mi</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/dp/B0GH912PFJ?psc=1</t>
+          <t>https://www.amazon.de/dp/B0D9BQHSWQ?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51GeVSsTnnL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/619CHOWba4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0GH912PFJ</t>
+          <t>B0D9BQHSWQ</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
@@ -18682,13 +18638,13 @@
         </is>
       </c>
       <c r="O50" s="15">
-        <v>73472</v>
+        <v>509144</v>
       </c>
       <c r="P50" s="15">
-        <v>737201</v>
+        <v>31748</v>
       </c>
       <c r="Q50" s="16">
-        <v>0.88</v>
+        <v>0.06</v>
       </c>
       <c r="R50" s="17" t="inlineStr">
         <is>
@@ -18697,86 +18653,106 @@
       </c>
       <c r="S50" s="18" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>6</v>
-      </c>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15">
-        <v>60</v>
-      </c>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="T50" s="15"/>
+      <c r="U50" s="16">
+        <v>-1</v>
+      </c>
+      <c r="V50" s="15"/>
       <c r="W50" s="15"/>
       <c r="X50" s="15"/>
       <c r="Y50" s="19">
         <v>1</v>
       </c>
       <c r="Z50" s="20">
-        <v>9.63</v>
+        <v>119.99</v>
       </c>
       <c r="AA50"/>
       <c r="AB50"/>
       <c r="AC50" s="2"/>
       <c r="AD50" s="19">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="AE50" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF50" s="21">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AG50" s="22">
         <v>0</v>
       </c>
       <c r="AH50" s="20">
-        <v>3.08</v>
+        <v>5.29</v>
       </c>
       <c r="AI50" s="16">
-        <v>0.54</v>
+        <v>0.81</v>
       </c>
       <c r="AJ50"/>
       <c r="AK50" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AL50" s="19">
-        <v>225</v>
+        <v>797</v>
       </c>
       <c r="AM50" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN50" s="13"/>
       <c r="AO50" s="13"/>
       <c r="AP50"/>
-      <c r="AQ50" s="19"/>
+      <c r="AQ50" s="19">
+        <v>10</v>
+      </c>
       <c r="AR50" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS50" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>NEXO HOME</t>
         </is>
       </c>
       <c r="AT50" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU50" s="13" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AV50" s="14" t="inlineStr">
+        <is>
+          <t>Barcelona Barcelona 08013 ES</t>
+        </is>
+      </c>
+      <c r="AW50" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UUYGTGLOQBB0</t>
+        </is>
+      </c>
       <c r="AX50" s="13"/>
       <c r="AY50" s="13"/>
       <c r="AZ50" s="13"/>
       <c r="BA50" s="13"/>
       <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
-      <c r="BD50" s="13"/>
+      <c r="BC50" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD50" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE50" s="13"/>
       <c r="BF50" s="13"/>
       <c r="BG50" s="13"/>
@@ -18784,265 +18760,45 @@
       <c r="BI50" s="23"/>
       <c r="BJ50" s="23" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>1.9 kg</t>
         </is>
       </c>
       <c r="BK50" s="23" t="inlineStr">
         <is>
-          <t>10.00 g</t>
+          <t>1.90 kg</t>
         </is>
       </c>
       <c r="BL50" s="23" t="inlineStr">
         <is>
-          <t>6.4 x 3.2 x 5 cm</t>
+          <t>20 x 26 x 32 cm</t>
         </is>
       </c>
       <c r="BM50" s="23" t="inlineStr">
         <is>
-          <t>6.40 x 3.20 x 5.00 cm</t>
+          <t>20.00 x 26.00 x 32.00 cm</t>
         </is>
       </c>
       <c r="BN50" s="23" t="inlineStr">
         <is>
-          <t>20 g</t>
+          <t>2.89 kg</t>
         </is>
       </c>
       <c r="BO50" s="23" t="inlineStr">
         <is>
-          <t>20.00 g</t>
+          <t>2.89 kg</t>
         </is>
       </c>
       <c r="BP50" s="23" t="inlineStr">
         <is>
-          <t>9.6 x 6.6 x 4.7 cm</t>
+          <t>38.7 x 31.5 x 20.2 cm</t>
         </is>
       </c>
       <c r="BQ50" s="23" t="inlineStr">
         <is>
-          <t>9.60 x 6.60 x 4.70 cm</t>
+          <t>38.70 x 31.50 x 20.20 cm</t>
         </is>
       </c>
       <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>超大号信封</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0D9BQHSWQ</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>Jimmy</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/stores/Jimmy/page/5E6E99F6-7A7E-4436-AC80-BC0EF24EA864?lp_asin=B0D9BQHSWQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Jimmy Milbensauger für Matratzen 15kPa Matratzensauger mit Staubsensor, Heißluftfunktion, UV-C Licht, Ultraschall-Technik, Mi</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/dp/B0D9BQHSWQ?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/619CHOWba4L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0D9BQHSWQ</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Küche, Haushalt &amp; Wohnen:Haushaltsreiniger &amp; Staubsauger:Staubsauger:Matratzensauger</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Küche, Haushalt &amp; Wohnen</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>509144</v>
-      </c>
-      <c r="P51" s="15">
-        <v>31748</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>0.06</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Matratzensauger</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16">
-        <v>-1</v>
-      </c>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>119.99</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>137</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>3</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>5.29</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.81</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>797</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>NEXO HOME</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AV51" s="14" t="inlineStr">
-        <is>
-          <t>Barcelona Barcelona 08013 ES</t>
-        </is>
-      </c>
-      <c r="AW51" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UUYGTGLOQBB0</t>
-        </is>
-      </c>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>1.9 kg</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>1.90 kg</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>20 x 26 x 32 cm</t>
-        </is>
-      </c>
-      <c r="BM51" s="23" t="inlineStr">
-        <is>
-          <t>20.00 x 26.00 x 32.00 cm</t>
-        </is>
-      </c>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>2.89 kg</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>2.89 kg</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>38.7 x 31.5 x 20.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>38.70 x 31.50 x 20.20 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
@@ -19429,23 +19185,16 @@
     <hyperlink ref="M49" r:id="rId375" tooltip="https://www.amazon.de/b?node=13528288031"/>
     <hyperlink ref="N49" r:id="rId376"/>
     <hyperlink ref="AW49" r:id="rId377" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ"/>
-    <hyperlink ref="C50" r:id="rId378" tooltip="https://www.amazon.de/dp/B0GH912PFJ"/>
-    <hyperlink ref="G50" r:id="rId379" tooltip="https://www.amazon.de/stores/K%C3%A4rcher/page/EFE3653A-1163-432C-A85B-0486A31C0E3D?lp_asin=B0GH912PFJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J50" r:id="rId380" tooltip="https://www.amazon.de/dp/B0GH912PFJ?psc=1"/>
-    <hyperlink ref="K50" r:id="rId381" tooltip="https://m.media-amazon.com/images/I/51GeVSsTnnL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId382" tooltip="https://www.amazon.de/dp/B0GH912PFJ"/>
+    <hyperlink ref="C50" r:id="rId378" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ"/>
+    <hyperlink ref="G50" r:id="rId379" tooltip="https://www.amazon.de/stores/Jimmy/page/5E6E99F6-7A7E-4436-AC80-BC0EF24EA864?lp_asin=B0D9BQHSWQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J50" r:id="rId380" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ?psc=1"/>
+    <hyperlink ref="K50" r:id="rId381" tooltip="https://images-na.ssl-images-amazon.com/images/I/619CHOWba4L._AC_US600_.jpg"/>
+    <hyperlink ref="L50" r:id="rId382" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ"/>
     <hyperlink ref="M50" r:id="rId383" tooltip="https://www.amazon.de/b?node=13528288031"/>
     <hyperlink ref="N50" r:id="rId384"/>
-    <hyperlink ref="C51" r:id="rId385" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ"/>
-    <hyperlink ref="G51" r:id="rId386" tooltip="https://www.amazon.de/stores/Jimmy/page/5E6E99F6-7A7E-4436-AC80-BC0EF24EA864?lp_asin=B0D9BQHSWQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J51" r:id="rId387" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ?psc=1"/>
-    <hyperlink ref="K51" r:id="rId388" tooltip="https://images-na.ssl-images-amazon.com/images/I/619CHOWba4L._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId389" tooltip="https://www.amazon.de/dp/B0D9BQHSWQ"/>
-    <hyperlink ref="M51" r:id="rId390" tooltip="https://www.amazon.de/b?node=13528288031"/>
-    <hyperlink ref="N51" r:id="rId391"/>
-    <hyperlink ref="AW51" r:id="rId392" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UUYGTGLOQBB0"/>
+    <hyperlink ref="AW50" r:id="rId385" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UUYGTGLOQBB0"/>
   </hyperlinks>
-  <drawing r:id="rId393"/>
+  <drawing r:id="rId386"/>
 </worksheet>
 </file>
 
@@ -19515,7 +19264,7 @@
         <v>165.79637618636755</v>
       </c>
       <c r="G2" s="22">
-        <v>0.1167758186397985</v>
+        <v>0.11684645629599757</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19536,7 +19285,7 @@
         <v>116.21190130624093</v>
       </c>
       <c r="G3" s="22">
-        <v>0.1388413098236776</v>
+        <v>0.13892529488859764</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19557,7 +19306,7 @@
         <v>59.98985959438377</v>
       </c>
       <c r="G4" s="22">
-        <v>0.12916876574307304</v>
+        <v>0.12924689988910174</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19578,7 +19327,7 @@
         <v>63.6396292004635</v>
       </c>
       <c r="G5" s="22">
-        <v>0.08695214105793451</v>
+        <v>0.08700473838088517</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19588,18 +19337,18 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C6" s="15">
-        <v>49494</v>
+        <v>49434</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="20">
-        <v>96.10485436893204</v>
+        <v>97.11984282907662</v>
       </c>
       <c r="G6" s="22">
-        <v>0.05188916876574307</v>
+        <v>0.05131565682024398</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19620,7 +19369,7 @@
         <v>33.88628762541806</v>
       </c>
       <c r="G7" s="22">
-        <v>0.12050377833753148</v>
+        <v>0.12057667103538663</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19641,7 +19390,7 @@
         <v>92.51948051948052</v>
       </c>
       <c r="G8" s="22">
-        <v>0.038790931989924435</v>
+        <v>0.03881439661256175</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19662,7 +19411,7 @@
         <v>69.0</v>
       </c>
       <c r="G9" s="22">
-        <v>0.048866498740554154</v>
+        <v>0.048896058070369994</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19683,7 +19432,7 @@
         <v>87.53672316384181</v>
       </c>
       <c r="G10" s="22">
-        <v>0.03566750629722922</v>
+        <v>0.03568908156064119</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19704,7 +19453,7 @@
         <v>66.84010152284264</v>
       </c>
       <c r="G11" s="22">
-        <v>0.03969773299748111</v>
+        <v>0.039721746143764496</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19725,7 +19474,7 @@
         <v>55.98882681564246</v>
       </c>
       <c r="G12" s="22">
-        <v>0.018035264483627203</v>
+        <v>0.01804617400947676</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19746,7 +19495,7 @@
         <v>64.59060402684564</v>
       </c>
       <c r="G13" s="22">
-        <v>0.015012594458438288</v>
+        <v>0.015021675572134288</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19767,7 +19516,7 @@
         <v>49.10928961748634</v>
       </c>
       <c r="G14" s="22">
-        <v>0.018438287153652394</v>
+        <v>0.018449440467789093</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19788,7 +19537,7 @@
         <v>89.98979591836735</v>
       </c>
       <c r="G15" s="22">
-        <v>0.009874055415617129</v>
+        <v>0.009880028228652082</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19809,7 +19558,7 @@
         <v>79.47058823529412</v>
       </c>
       <c r="G16" s="22">
-        <v>0.010277078085642318</v>
+        <v>0.010283294686964413</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19830,7 +19579,7 @@
         <v>99.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.007858942065491184</v>
+        <v>0.007863695937090432</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19851,7 +19600,7 @@
         <v>59.99212598425197</v>
       </c>
       <c r="G18" s="22">
-        <v>0.012795969773299748</v>
+        <v>0.012803710051416473</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19872,7 +19621,7 @@
         <v>109.9047619047619</v>
       </c>
       <c r="G19" s="22">
-        <v>0.006347607052896725</v>
+        <v>0.006351446718419196</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19893,7 +19642,7 @@
         <v>89.98507462686567</v>
       </c>
       <c r="G20" s="22">
-        <v>0.006750629722921914</v>
+        <v>0.006754713176731525</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19914,7 +19663,7 @@
         <v>99.98245614035088</v>
       </c>
       <c r="G21" s="22">
-        <v>0.005743073047858942</v>
+        <v>0.005746547030950701</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19935,7 +19684,7 @@
         <v>29.865921787709496</v>
       </c>
       <c r="G22" s="22">
-        <v>0.018035264483627203</v>
+        <v>0.01804617400947676</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19956,7 +19705,7 @@
         <v>56.22352941176471</v>
       </c>
       <c r="G23" s="22">
-        <v>0.008564231738035265</v>
+        <v>0.008569412239137009</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19977,7 +19726,7 @@
         <v>69.98461538461538</v>
       </c>
       <c r="G24" s="22">
-        <v>0.00654911838790932</v>
+        <v>0.00655307994757536</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19998,7 +19747,7 @@
         <v>25.517241379310345</v>
       </c>
       <c r="G25" s="22">
-        <v>0.014609571788413099</v>
+        <v>0.014618409113821958</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20019,7 +19768,7 @@
         <v>69.91111111111111</v>
       </c>
       <c r="G26" s="22">
-        <v>0.004534005037783375</v>
+        <v>0.004536747656013711</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20040,7 +19789,7 @@
         <v>29.897727272727273</v>
       </c>
       <c r="G27" s="22">
-        <v>0.008866498740554157</v>
+        <v>0.008871862082871258</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20061,7 +19810,7 @@
         <v>53.3469387755102</v>
       </c>
       <c r="G28" s="22">
-        <v>0.0049370277078085644</v>
+        <v>0.004940014114326041</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20082,7 +19831,7 @@
         <v>80.0</v>
       </c>
       <c r="G29" s="22">
-        <v>0.0020151133501259445</v>
+        <v>0.0020163322915616494</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20103,7 +19852,7 @@
         <v>89.38461538461539</v>
       </c>
       <c r="G30" s="22">
-        <v>0.001309823677581864</v>
+        <v>0.001310615989515072</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20124,7 +19873,7 @@
         <v>29.83783783783784</v>
       </c>
       <c r="G31" s="22">
-        <v>0.0037279596977329976</v>
+        <v>0.003730214739389051</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20145,7 +19894,7 @@
         <v>60.0</v>
       </c>
       <c r="G32" s="22">
-        <v>0.0017128463476070528</v>
+        <v>0.001713882447827402</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20166,7 +19915,7 @@
         <v>39.92</v>
       </c>
       <c r="G33" s="22">
-        <v>0.0025188916876574307</v>
+        <v>0.0025204153644520617</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20187,7 +19936,7 @@
         <v>20.0</v>
       </c>
       <c r="G34" s="22">
-        <v>0.002115869017632242</v>
+        <v>0.002117148906139732</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20208,7 +19957,7 @@
         <v>20.0</v>
       </c>
       <c r="G35" s="22">
-        <v>0.0012090680100755667</v>
+        <v>0.0012097993749369896</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20229,7 +19978,7 @@
         <v>20.142857142857142</v>
       </c>
       <c r="G36" s="22">
-        <v>0.0007052896725440807</v>
+        <v>0.0007057163020465773</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20250,7 +19999,7 @@
         <v>30.0</v>
       </c>
       <c r="G37" s="22">
-        <v>0.00030226700251889167</v>
+        <v>0.0003024498437342474</v>
       </c>
     </row>
   </sheetData>
@@ -20314,18 +20063,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>3644</v>
+        <v>3638</v>
       </c>
       <c r="C2" s="15">
-        <v>280797</v>
+        <v>280737</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>77.05735455543359</v>
+        <v>77.16794942275976</v>
       </c>
       <c r="G2" s="22">
-        <v>0.3671536523929471</v>
+        <v>0.36677084383506403</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20346,7 +20095,7 @@
         <v>165.79637618636755</v>
       </c>
       <c r="G3" s="22">
-        <v>0.1167758186397985</v>
+        <v>0.11684645629599757</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20367,7 +20116,7 @@
         <v>59.98985959438377</v>
       </c>
       <c r="G4" s="22">
-        <v>0.12916876574307304</v>
+        <v>0.12924689988910174</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20388,7 +20137,7 @@
         <v>63.6396292004635</v>
       </c>
       <c r="G5" s="22">
-        <v>0.08695214105793451</v>
+        <v>0.08700473838088517</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20409,7 +20158,7 @@
         <v>92.51948051948052</v>
       </c>
       <c r="G6" s="22">
-        <v>0.038790931989924435</v>
+        <v>0.03881439661256175</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20430,7 +20179,7 @@
         <v>69.0</v>
       </c>
       <c r="G7" s="22">
-        <v>0.048866498740554154</v>
+        <v>0.048896058070369994</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20451,7 +20200,7 @@
         <v>88.87894736842105</v>
       </c>
       <c r="G8" s="22">
-        <v>0.019143576826196475</v>
+        <v>0.01915515676983567</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20472,7 +20221,7 @@
         <v>85.98170731707317</v>
       </c>
       <c r="G9" s="22">
-        <v>0.016523929471032747</v>
+        <v>0.016533924790805524</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20493,7 +20242,7 @@
         <v>55.98882681564246</v>
       </c>
       <c r="G10" s="22">
-        <v>0.018035264483627203</v>
+        <v>0.01804617400947676</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20514,7 +20263,7 @@
         <v>64.59060402684564</v>
       </c>
       <c r="G11" s="22">
-        <v>0.015012594458438288</v>
+        <v>0.015021675572134288</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20535,7 +20284,7 @@
         <v>49.10928961748634</v>
       </c>
       <c r="G12" s="22">
-        <v>0.018438287153652394</v>
+        <v>0.018449440467789093</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20556,7 +20305,7 @@
         <v>89.98979591836735</v>
       </c>
       <c r="G13" s="22">
-        <v>0.009874055415617129</v>
+        <v>0.009880028228652082</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20577,7 +20326,7 @@
         <v>79.47058823529412</v>
       </c>
       <c r="G14" s="22">
-        <v>0.010277078085642318</v>
+        <v>0.010283294686964413</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20598,7 +20347,7 @@
         <v>99.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.007858942065491184</v>
+        <v>0.007863695937090432</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20619,7 +20368,7 @@
         <v>59.99212598425197</v>
       </c>
       <c r="G16" s="22">
-        <v>0.012795969773299748</v>
+        <v>0.012803710051416473</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20640,7 +20389,7 @@
         <v>109.9047619047619</v>
       </c>
       <c r="G17" s="22">
-        <v>0.006347607052896725</v>
+        <v>0.006351446718419196</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20661,7 +20410,7 @@
         <v>89.98507462686567</v>
       </c>
       <c r="G18" s="22">
-        <v>0.006750629722921914</v>
+        <v>0.006754713176731525</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20682,7 +20431,7 @@
         <v>99.98245614035088</v>
       </c>
       <c r="G19" s="22">
-        <v>0.005743073047858942</v>
+        <v>0.005746547030950701</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20703,7 +20452,7 @@
         <v>56.22352941176471</v>
       </c>
       <c r="G20" s="22">
-        <v>0.008564231738035265</v>
+        <v>0.008569412239137009</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20724,7 +20473,7 @@
         <v>69.98461538461538</v>
       </c>
       <c r="G21" s="22">
-        <v>0.00654911838790932</v>
+        <v>0.00655307994757536</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20745,7 +20494,7 @@
         <v>29.849206349206348</v>
       </c>
       <c r="G22" s="22">
-        <v>0.01269521410579345</v>
+        <v>0.012702893436838392</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20766,7 +20515,7 @@
         <v>69.91111111111111</v>
       </c>
       <c r="G23" s="22">
-        <v>0.004534005037783375</v>
+        <v>0.004536747656013711</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20787,7 +20536,7 @@
         <v>29.897727272727273</v>
       </c>
       <c r="G24" s="22">
-        <v>0.008866498740554157</v>
+        <v>0.008871862082871258</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20808,7 +20557,7 @@
         <v>53.3469387755102</v>
       </c>
       <c r="G25" s="22">
-        <v>0.0049370277078085644</v>
+        <v>0.004940014114326041</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20829,7 +20578,7 @@
         <v>31.983870967741936</v>
       </c>
       <c r="G26" s="22">
-        <v>0.006246851385390428</v>
+        <v>0.006250630103841113</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20850,7 +20599,7 @@
         <v>80.0</v>
       </c>
       <c r="G27" s="22">
-        <v>0.0020151133501259445</v>
+        <v>0.0020163322915616494</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20871,7 +20620,7 @@
         <v>89.38461538461539</v>
       </c>
       <c r="G28" s="22">
-        <v>0.001309823677581864</v>
+        <v>0.001310615989515072</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20892,7 +20641,7 @@
         <v>29.83783783783784</v>
       </c>
       <c r="G29" s="22">
-        <v>0.0037279596977329976</v>
+        <v>0.003730214739389051</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20913,7 +20662,7 @@
         <v>60.0</v>
       </c>
       <c r="G30" s="22">
-        <v>0.0017128463476070528</v>
+        <v>0.001713882447827402</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20934,7 +20683,7 @@
         <v>20.0</v>
       </c>
       <c r="G31" s="22">
-        <v>0.002115869017632242</v>
+        <v>0.002117148906139732</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20955,7 +20704,7 @@
         <v>20.0</v>
       </c>
       <c r="G32" s="22">
-        <v>0.0012090680100755667</v>
+        <v>0.0012097993749369896</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20976,7 +20725,7 @@
         <v>20.142857142857142</v>
       </c>
       <c r="G33" s="22">
-        <v>0.0007052896725440807</v>
+        <v>0.0007057163020465773</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20997,7 +20746,7 @@
         <v>30.0</v>
       </c>
       <c r="G34" s="22">
-        <v>0.00030226700251889167</v>
+        <v>0.0003024498437342474</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
